--- a/hotel_manager_forms/013_hostel_management_routine_check_form--hotel_manager_forms.xlsx
+++ b/hotel_manager_forms/013_hostel_management_routine_check_form--hotel_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>completed_status</t>
+          <t>completed_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Completed Status</t>
+          <t>Completed Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>routine_status</t>
+          <t>routine_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>completed_status_choices</t>
+          <t>completed_status_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>completed_status_choices</t>
+          <t>completed_status_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>completed_status_choices</t>
+          <t>completed_status_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>completed_status_choices</t>
+          <t>completed_status_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>routine_status_choices</t>
+          <t>routine_status_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>routine_status_choices</t>
+          <t>routine_status_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>routine_status_choices</t>
+          <t>routine_status_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>routine_status_choices</t>
+          <t>routine_status_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
